--- a/artfynd/A 49372-2024 artfynd.xlsx
+++ b/artfynd/A 49372-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80675798</v>
+        <v>120599319</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Störrestjärnen, Jmt</t>
+          <t>Störrestjärn, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513060.8434472426</v>
+        <v>513037</v>
       </c>
       <c r="R2" t="n">
-        <v>6944955.101092148</v>
+        <v>6944670</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,49 +764,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120596170</v>
+        <v>120608177</v>
       </c>
       <c r="B3" t="n">
-        <v>91241</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513041</v>
+        <v>513053</v>
       </c>
       <c r="R3" t="n">
-        <v>6944311</v>
+        <v>6944953</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120608280</v>
+        <v>120596156</v>
       </c>
       <c r="B4" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512993</v>
+        <v>513023</v>
       </c>
       <c r="R4" t="n">
-        <v>6944966</v>
+        <v>6944230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120607791</v>
+        <v>120596170</v>
       </c>
       <c r="B5" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513120</v>
+        <v>513041</v>
       </c>
       <c r="R5" t="n">
-        <v>6944790</v>
+        <v>6944311</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120596184</v>
+        <v>120596187</v>
       </c>
       <c r="B6" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512940</v>
+        <v>512908</v>
       </c>
       <c r="R6" t="n">
-        <v>6944370</v>
+        <v>6944497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120607872</v>
+        <v>80675798</v>
       </c>
       <c r="B7" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,37 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Störrestjärn, Jmt</t>
+          <t>Störrestjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513146</v>
+        <v>513061</v>
       </c>
       <c r="R7" t="n">
-        <v>6944789</v>
+        <v>6944955</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2019-07-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2019-07-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,31 +1266,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120607963</v>
+        <v>120596174</v>
       </c>
       <c r="B8" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1361,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513197</v>
+        <v>512920</v>
       </c>
       <c r="R8" t="n">
-        <v>6944791</v>
+        <v>6944334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,37 +1379,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120596187</v>
+        <v>120596184</v>
       </c>
       <c r="B9" t="n">
-        <v>91119</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512908</v>
+        <v>512940</v>
       </c>
       <c r="R9" t="n">
-        <v>6944497</v>
+        <v>6944370</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,15 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120608253</v>
+        <v>120600263</v>
       </c>
       <c r="B10" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,21 +1491,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512993</v>
+        <v>513075</v>
       </c>
       <c r="R10" t="n">
-        <v>6944966</v>
+        <v>6944619</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,19 +1581,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120596174</v>
+        <v>120607671</v>
       </c>
       <c r="B11" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1679,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512920</v>
+        <v>513109</v>
       </c>
       <c r="R11" t="n">
-        <v>6944334</v>
+        <v>6944763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,15 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120596151</v>
+        <v>120607963</v>
       </c>
       <c r="B12" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513064</v>
+        <v>513197</v>
       </c>
       <c r="R12" t="n">
-        <v>6944205</v>
+        <v>6944791</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,37 +1783,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120607671</v>
+        <v>120608280</v>
       </c>
       <c r="B13" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513109</v>
+        <v>512993</v>
       </c>
       <c r="R13" t="n">
-        <v>6944763</v>
+        <v>6944966</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,37 +1884,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120596156</v>
+        <v>120596151</v>
       </c>
       <c r="B14" t="n">
-        <v>91241</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513023</v>
+        <v>513064</v>
       </c>
       <c r="R14" t="n">
-        <v>6944230</v>
+        <v>6944205</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,12 +1988,7 @@
         <v>120596153</v>
       </c>
       <c r="B15" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,15 +2086,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120608177</v>
+        <v>120600227</v>
       </c>
       <c r="B16" t="n">
-        <v>88012</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,21 +2097,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513053</v>
+        <v>513075</v>
       </c>
       <c r="R16" t="n">
-        <v>6944953</v>
+        <v>6944619</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,6 +2184,531 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120607791</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Störrestjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>513120</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6944790</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120607872</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Störrestjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>513146</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6944789</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120600001</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Störrestjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>513053</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6944664</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack i tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120599527</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Störrestjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>513040</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6944670</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126190230</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Störretjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>513046</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6944663</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Uppdelat på två bestånd, vid lokalens koordinat och cirka tio meter NV om denna, växandes utefter en sten. Totalt två florala. Vid lokalen har traktorväg brutits för avverkning. Som närmast går traktorvägen ca 15 m sydost om lokalen.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lars Grönvik</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49372-2024 artfynd.xlsx
+++ b/artfynd/A 49372-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596187</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596174</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596184</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120599319</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120608177</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596156</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596170</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675798</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1578,6 +1623,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120600263</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1679,6 +1729,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120607671</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1780,6 +1835,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120607963</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120608280</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1982,6 +2047,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596151</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2083,6 +2153,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596153</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2184,6 +2259,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120600227</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2285,6 +2365,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120607791</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2386,6 +2471,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120607872</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2492,6 +2582,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120600001</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2594,6 +2689,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120599527</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2709,8 +2809,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126190230</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>